--- a/out/LSTM-Mamba1_repeat_3_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7769695850834732</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7769695850834732</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>4.409276425334538</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>4.409276425334538</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>4.409276425334538</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>4.409276425334538</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>4.409276425334538</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>4.409276425334538</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>4.409276425334538</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>4.409276425334538</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>4.409276425334538</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>4.409276425334538</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>4.409276425334538</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0004499998998588417</v>
+        <v>-6.522884500527289e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1937568916215206</v>
+        <v>0.02808564681070064</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>4.409276425334538</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3880308691591267</v>
+        <v>0.05624624678713619</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7485845139206162</v>
+        <v>0.1085088794383322</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.409276425334538</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.69194014772856</v>
+        <v>0.2452518374137715</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2302687928309839</v>
+        <v>0.03337793958473097</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.402944936957548</v>
+        <v>0.2033608363725715</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04672325095406269</v>
+        <v>0.006772323509422399</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.265761806680401</v>
+        <v>0.1834748228730182</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.04046441184238865</v>
+        <v>0.005863566622783443</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.29991602913028</v>
+        <v>0.1884236426376505</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01978213259579021</v>
+        <v>0.002863672648104922</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.29896367110327</v>
+        <v>0.1882820691942722</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.009440942066222488</v>
+        <v>0.001364083631158653</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.298037343944809</v>
+        <v>0.188143505866406</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0039303844252945</v>
+        <v>0.0005656279581166873</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.296445657029138</v>
+        <v>0.187908437385919</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002722087045752315</v>
+        <v>0.0003900958028933744</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.297956655837964</v>
+        <v>0.1881232567927102</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001133455170814947</v>
+        <v>0.0001599374780580794</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.297498387069153</v>
+        <v>0.1880524789126902</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005856637042187651</v>
+        <v>8.052596622172162e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.297534427868099</v>
+        <v>0.1880534453850971</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002269899262110028</v>
+        <v>2.859130153281488e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.297402048971632</v>
+        <v>0.1880298579022884</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001215519507552314</v>
+        <v>1.332426436274844e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.297417904209835</v>
+        <v>0.1880279254918529</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.711389054071077e-05</v>
+        <v>4.034747715012475e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.29741100224076</v>
+        <v>0.1880226420301429</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.430540885788129e-05</v>
+        <v>-7.373950752172664e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.297402395000589</v>
+        <v>0.1880170900940134</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>7.912811891542016e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.297393345323467</v>
+        <v>0.1880114398288601</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>7.876374973718185e-07</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.297386990860328</v>
+        <v>0.1880061985075593</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.774949699713269e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.29738064486031</v>
+        <v>0.1880009105687088</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.29737469384955</v>
+        <v>0.1879956387346578</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.555348042317843e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.297369851542107</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.297364930340559</v>
+        <v>0.1879957184456023</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.297364922369465</v>
+        <v>0.1879957104745079</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.297365081791354</v>
+        <v>0.187995869896397</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.297365336866377</v>
+        <v>0.1879961249714198</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.297365089762448</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.297365049906976</v>
+        <v>0.1879958380120192</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.29736505787807</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.297365089762448</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.297365185415582</v>
+        <v>0.1879959735206251</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.297365121646826</v>
+        <v>0.1879959097518693</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.297365081791354</v>
+        <v>0.187995869896397</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.29736505787807</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.297364810774142</v>
+        <v>0.1879955988791855</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.297364731063198</v>
+        <v>0.1879955191682407</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.297364778889765</v>
+        <v>0.1879955669948075</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.297364898456181</v>
+        <v>0.1879956865612245</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.297364882513993</v>
+        <v>0.1879956706190356</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.297364898456181</v>
+        <v>0.1879956865612245</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.297364882513993</v>
+        <v>0.1879956706190356</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.297364938311654</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.297364938311654</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.297364938311654</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.297365089762448</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.297365304981999</v>
+        <v>0.187996093087042</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.29736521729996</v>
+        <v>0.187996005405003</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.297365169473393</v>
+        <v>0.1879959575784362</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.29736521729996</v>
+        <v>0.187996005405003</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.297365033964787</v>
+        <v>0.1879958220698303</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.297365041935882</v>
+        <v>0.1879958300409247</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.297365049906976</v>
+        <v>0.1879958380120192</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.29736505787807</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.29736505787807</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.297365097733543</v>
+        <v>0.1879958858385859</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.297365161502299</v>
+        <v>0.1879959496073418</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.297365273097621</v>
+        <v>0.1879960612026642</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.297365320924188</v>
+        <v>0.1879961090292309</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.297365281068715</v>
+        <v>0.1879960691737586</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.297365209328865</v>
+        <v>0.1879959974339085</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.297365328895282</v>
+        <v>0.1879961170003253</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.297365169473393</v>
+        <v>0.1879959575784362</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.297364938311654</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.297364890485087</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.297364922369465</v>
+        <v>0.1879957104745079</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.297364906427276</v>
+        <v>0.187995694532319</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.297364786860859</v>
+        <v>0.1879955749659019</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.297364747005387</v>
+        <v>0.1879955351104296</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.297364890485087</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.297365025993693</v>
+        <v>0.1879958140987358</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.297365010051504</v>
+        <v>0.1879957981565469</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.297364946282748</v>
+        <v>0.1879957343877912</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.29736484265852</v>
+        <v>0.1879956307635633</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.297364723092103</v>
+        <v>0.1879955111971462</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.29736484265852</v>
+        <v>0.1879956307635633</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.297364890485087</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.29736498613822</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.297364866571804</v>
+        <v>0.1879956546768467</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.297364874542898</v>
+        <v>0.1879956626479412</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_3_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7769695850834732</v>
+        <v>0.8812199440383068</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>4.409276425334538</v>
+        <v>1.929504746419567</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>4.409276425334538</v>
+        <v>2.977789548800827</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>4.409276425334538</v>
+        <v>2.977789548800827</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>4.409276425334538</v>
+        <v>2.977789548800827</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>4.409276425334538</v>
+        <v>1.929504746419567</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1769695850834732</v>
+        <v>0.8812199440383068</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7769695850834732</v>
+        <v>0.8812199440383068</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>4.409276425334538</v>
+        <v>1.929504746419567</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>4.409276425334538</v>
+        <v>2.977789548800827</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>4.409276425334538</v>
+        <v>2.977789548800827</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>4.409276425334538</v>
+        <v>2.977789548800827</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>4.409276425334538</v>
+        <v>2.977789548800827</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>4.409276425334538</v>
+        <v>2.977789548800827</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0004499998998588417</v>
+        <v>-0.0003432120308016892</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1937568916215206</v>
+        <v>0.1477770285998284</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>4.409276425334538</v>
+        <v>2.977789548800827</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3880308691591267</v>
+        <v>0.2959486499888853</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7485845139206162</v>
+        <v>0.5709416412219356</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.409276425334538</v>
+        <v>1.929504746419567</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.69194014772856</v>
+        <v>1.290432593926715</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2302687928309839</v>
+        <v>0.1756243403623346</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7769695850834732</v>
+        <v>0.681219944038307</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.402944936957548</v>
+        <v>1.070017888652805</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04672325095406269</v>
+        <v>0.03563569163184852</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.265761806680401</v>
+        <v>0.9653891644178577</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.04046441184238865</v>
+        <v>0.03086209270620323</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.29991602913028</v>
+        <v>0.9914382624619652</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01978213259579021</v>
+        <v>0.01508742686905355</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.29896367110327</v>
+        <v>0.9907119147408597</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.009440942066222488</v>
+        <v>0.007199226310957833</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.298037343944809</v>
+        <v>0.9900042298434547</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0039303844252945</v>
+        <v>0.002996224704592255</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.296445657029138</v>
+        <v>0.9887890702692979</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002722087045752315</v>
+        <v>0.002075426337110425</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.297956655837964</v>
+        <v>0.9899404235677377</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001133455170814947</v>
+        <v>0.0008634989078995742</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.297498387069153</v>
+        <v>0.9895897334829657</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0005856637042187651</v>
+        <v>0.0004453476658862529</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.297534427868099</v>
+        <v>0.9896160247708503</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002269899262110028</v>
+        <v>0.0001718791971337284</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.297402048971632</v>
+        <v>0.9895139055669829</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001215519507552314</v>
+        <v>9.120238790442933e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.297417904209835</v>
+        <v>0.9895248071492876</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.711389054071077e-05</v>
+        <v>4.243242550381549e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.29741100224076</v>
+        <v>0.9895183528524624</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.430540885788129e-05</v>
+        <v>1.737867585510935e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.297402395000589</v>
+        <v>0.9895105906963875</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>7.912811891542016e-06</v>
+        <v>4.684608918656512e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.297393345323467</v>
+        <v>0.9895024816986963</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>7.876374973718185e-07</v>
+        <v>-4.525705377792857e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.297386990860328</v>
+        <v>0.989496417477658</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.774949699713269e-06</v>
+        <v>-3.410678356938051e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.29738064486031</v>
+        <v>0.9894903603959401</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.29737469384955</v>
+        <v>0.9894845448937866</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.555348042317843e-06</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.297369851542107</v>
+        <v>0.9894796635955372</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.297364930340559</v>
+        <v>0.9894747423939894</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.297364922369465</v>
+        <v>0.9894747344228949</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.297365081791354</v>
+        <v>0.989474893844784</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.29736498613822</v>
+        <v>0.9894747981916505</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.297365336866377</v>
+        <v>0.9894751489198068</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.297365089762448</v>
+        <v>0.9894749018158785</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.297365049906976</v>
+        <v>0.9894748619604061</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.29736498613822</v>
+        <v>0.9894747981916505</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.29736505787807</v>
+        <v>0.9894748699315007</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.29736498613822</v>
+        <v>0.9894747981916505</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.297365089762448</v>
+        <v>0.9894749018158785</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.297365185415582</v>
+        <v>0.9894749974690121</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.297365121646826</v>
+        <v>0.9894749337002563</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.297365081791354</v>
+        <v>0.989474893844784</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.29736505787807</v>
+        <v>0.9894748699315007</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.297364810774142</v>
+        <v>0.9894746228275725</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.297364731063198</v>
+        <v>0.9894745431166277</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.297364778889765</v>
+        <v>0.9894745909431945</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.297364898456181</v>
+        <v>0.9894747105096116</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.297364882513993</v>
+        <v>0.9894746945674227</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.297364898456181</v>
+        <v>0.9894747105096116</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.297364882513993</v>
+        <v>0.9894746945674227</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.297364938311654</v>
+        <v>0.9894747503650838</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.297364938311654</v>
+        <v>0.9894747503650838</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.297364938311654</v>
+        <v>0.9894747503650838</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.297365089762448</v>
+        <v>0.9894749018158785</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.297365304981999</v>
+        <v>0.989475117035429</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.29736521729996</v>
+        <v>0.9894750293533899</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.297365169473393</v>
+        <v>0.9894749815268232</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.29736521729996</v>
+        <v>0.9894750293533899</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.297365033964787</v>
+        <v>0.9894748460182172</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.297365041935882</v>
+        <v>0.9894748539893117</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.297365049906976</v>
+        <v>0.9894748619604061</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.29736505787807</v>
+        <v>0.9894748699315007</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.29736505787807</v>
+        <v>0.9894748699315007</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.297365097733543</v>
+        <v>0.9894749097869729</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.297365161502299</v>
+        <v>0.9894749735557288</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.297365273097621</v>
+        <v>0.9894750851510512</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.297365320924188</v>
+        <v>0.9894751329776179</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.297365281068715</v>
+        <v>0.9894750931221457</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.297365209328865</v>
+        <v>0.9894750213822955</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.297365328895282</v>
+        <v>0.9894751409487124</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.297365169473393</v>
+        <v>0.9894749815268232</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.297364938311654</v>
+        <v>0.9894747503650838</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.297364890485087</v>
+        <v>0.9894747025385171</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.297364922369465</v>
+        <v>0.9894747344228949</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.29736498613822</v>
+        <v>0.9894747981916505</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.29736498613822</v>
+        <v>0.9894747981916505</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.297364906427276</v>
+        <v>0.989474718480706</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.297364786860859</v>
+        <v>0.9894745989142889</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.297364747005387</v>
+        <v>0.9894745590588166</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.297364890485087</v>
+        <v>0.9894747025385171</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.297365025993693</v>
+        <v>0.9894748380471228</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.297365010051504</v>
+        <v>0.9894748221049339</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.29736498613822</v>
+        <v>0.9894747981916505</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.297364946282748</v>
+        <v>0.9894747583361783</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.29736484265852</v>
+        <v>0.9894746547119503</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.297364723092103</v>
+        <v>0.9894745351455333</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.29736484265852</v>
+        <v>0.9894746547119503</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.297364890485087</v>
+        <v>0.9894747025385171</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.29736498613822</v>
+        <v>0.9894747981916505</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.297364866571804</v>
+        <v>0.9894746786252338</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7769695850834732</v>
+        <v>-0.3670648583429531</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.297364874542898</v>
+        <v>0.9894746865963282</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_3_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.02270676754415035</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.01275349594652653</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.007287226617336273</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.004402559250593185</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.002684600651264191</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001435071229934692</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.001174002885818481</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.001004327088594437</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0005896426737308502</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0005423910915851593</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0003544092178344727</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0003115348517894745</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.8812199440383068</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>1.406297087669373e-05</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.929504746419567</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.000568833202123642</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.977789548800827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0009457394480705261</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.977789548800827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.0009815245866775513</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.977789548800827</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0003440901637077332</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.929504746419567</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-9.53376293182373e-05</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8812199440383068</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.0003711842000484467</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.0007322579622268677</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.00096922367811203</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.000963013619184494</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.0008318610489368439</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.0006316192448139191</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.000751301646232605</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0008632689714431763</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0008858516812324524</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.0009281188249588013</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.0006351768970489502</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-7.360056042671204e-05</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0003075525164604187</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0003825798630714417</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0005825720727443695</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.0005738735198974609</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.0004628486931324005</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0001195631921291351</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.8812199440383068</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0002593845129013062</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.929504746419567</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0005945265293121338</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.977789548800827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.001320123672485352</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.977789548800827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001892492175102234</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.977789548800827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.002637226134538651</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.977789548800827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.002910833805799484</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.977789548800827</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003432120308016892</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1477770285998284</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.003540072590112686</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.977789548800827</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2959486499888853</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5709416412219356</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.003219962120056152</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.929504746419567</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.290432593926715</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1756243403623346</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0001596100628376007</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.681219944038307</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.070017888652805</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03563569163184852</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.002885580062866211</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.9653891644178577</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03086209270620323</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.005471073091030121</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.9914382624619652</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01508742686905355</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.006203126162290573</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.9907119147408597</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007199226310957833</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.00642041489481926</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.9900042298434547</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002996224704592255</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.006232470273971558</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9887890702692979</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002075426337110425</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.006009846925735474</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.9899404235677377</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008634989078995742</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.005126237869262695</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.9895897334829657</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004453476658862529</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.004634961485862732</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.9896160247708503</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001718791971337284</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.00507669523358345</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.9895139055669829</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.120238790442933e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.005259372293949127</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.9895248071492876</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.243242550381549e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.005497049540281296</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.9895183528524624</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.737867585510935e-05</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.005204755812883377</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.9895105906963875</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.684608918656512e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.004766102880239487</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.9895024816986963</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.525705377792857e-07</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.004298564046621323</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.989496417477658</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003882508724927902</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.9894903603959401</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.003662660717964172</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.9894845448937866</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.003223203122615814</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.9894796635955372</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.003252118825912476</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.9894747423939894</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.002829082310199738</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.9894747344228949</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.002818945795297623</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.989474893844784</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.002250254154205322</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.9894747981916505</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.002437110990285873</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.9894751489198068</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.003146272152662277</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.9894749018158785</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.003403868526220322</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.9894748619604061</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.003820683807134628</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.9894747981916505</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.003910496830940247</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.9894748699315007</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.003817055374383926</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.9894747981916505</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.001854255795478821</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.9894749018158785</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.002065662294626236</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.9894749974690121</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.003355506807565689</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.9894749337002563</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004335477948188782</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.989474893844784</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.004356462508440018</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.9894748699315007</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.004399742931127548</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.9894746228275725</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.004301086068153381</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.9894745431166277</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.003883343189954758</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.9894745909431945</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.003523025661706924</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.9894747105096116</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.002988949418067932</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.9894746945674227</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.002690795809030533</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.9894747105096116</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.002415653318166733</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.9894746945674227</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.002366747707128525</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.9894747503650838</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.002559509128332138</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.9894747503650838</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.001953493803739548</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.9894747503650838</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.002156689763069153</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.9894749018158785</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.001661613583564758</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.989475117035429</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.002380520105361938</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.9894750293533899</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.002868436276912689</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.9894749815268232</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.003091830760240555</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.9894750293533899</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.003423728048801422</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.9894748460182172</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.003512397408485413</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.9894748539893117</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.003206048160791397</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.9894748619604061</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.003179304301738739</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.9894748699315007</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.003048095852136612</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.9894748699315007</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.002320911735296249</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.9894749097869729</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.002157095819711685</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.9894749735557288</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.002178966999053955</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.9894750851510512</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.002704165875911713</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.9894751329776179</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.002961795777082443</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.9894750931221457</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.002982009202241898</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.9894750213822955</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.003088101744651794</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.9894751409487124</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003165923058986664</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.9894749815268232</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.003617372363805771</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.9894747503650838</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.003813415765762329</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.9894747025385171</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.003846459090709686</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.9894747344228949</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.003479808568954468</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.9894747981916505</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.003375127911567688</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.9894747981916505</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003229197114706039</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.989474718480706</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003047917038202286</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.9894745989142889</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002762474119663239</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.9894745590588166</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002350185066461563</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.9894747025385171</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.002202562987804413</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.9894748380471228</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.002369016408920288</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.9894748221049339</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.002404466271400452</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.9894747981916505</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002424471080303192</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.9894747583361783</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.002322204411029816</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.9894746547119503</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.002017851918935776</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.9894745351455333</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.002281248569488525</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.9894746547119503</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.002268847078084946</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3670648583429531</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.9894747025385171</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002520866692066193</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.9894747981916505</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002594590187072754</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.2300000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.9894746786252338</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002326879650354385</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3670648583429531</v>
+        <v>-0.4400000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.9894746865963282</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_3_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.02270676754415035</v>
+        <v>-0.02270676381886005</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.01275349594652653</v>
+        <v>-0.01275350712239742</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.007287226617336273</v>
+        <v>-0.00728723406791687</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.004402559250593185</v>
+        <v>-0.00440254807472229</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.002684600651264191</v>
+        <v>-0.002684608101844788</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.4399999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.001435071229934692</v>
+        <v>-0.001435067504644394</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.16</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.001174002885818481</v>
+        <v>-0.001174010336399078</v>
       </c>
       <c r="JB8" t="n">
         <v>0.7199999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.001004327088594437</v>
+        <v>-0.00100431963801384</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0005896426737308502</v>
+        <v>-0.0005897432565689087</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.0005423910915851593</v>
+        <v>-0.0005423352122306824</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.0003544092178344727</v>
+        <v>-0.0003543831408023834</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0003115348517894745</v>
+        <v>-0.0003115199506282806</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.000568833202123642</v>
+        <v>0.0005688071250915527</v>
       </c>
       <c r="JB15" t="n">
         <v>0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.0009457394480705261</v>
+        <v>0.00094570592045784</v>
       </c>
       <c r="JB16" t="n">
         <v>0.9999999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.0009815245866775513</v>
+        <v>0.0009814910590648651</v>
       </c>
       <c r="JB17" t="n">
         <v>0.2599999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.0003440901637077332</v>
+        <v>0.0003439709544181824</v>
       </c>
       <c r="JB18" t="n">
         <v>0.1199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-9.53376293182373e-05</v>
+        <v>-9.542331099510193e-05</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.02000000000000007</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.0003711842000484467</v>
+        <v>-0.0003712363541126251</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.16</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.0007322579622268677</v>
+        <v>-0.0007322803139686584</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.3</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.00096922367811203</v>
+        <v>-0.0009692274034023285</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.3</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.000963013619184494</v>
+        <v>-0.000963062047958374</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.3</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.0008318610489368439</v>
+        <v>-0.0008318759500980377</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.0006316192448139191</v>
+        <v>-0.0006316453218460083</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.16</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.000751301646232605</v>
+        <v>-0.0007513128221035004</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.02000000000000007</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.0008632689714431763</v>
+        <v>-0.0008633174002170563</v>
       </c>
       <c r="JB27" t="n">
         <v>0.5799999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.0008858516812324524</v>
+        <v>-0.0008858665823936462</v>
       </c>
       <c r="JB28" t="n">
         <v>0.5799999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.0009281188249588013</v>
+        <v>-0.0009281300008296967</v>
       </c>
       <c r="JB29" t="n">
         <v>0.7199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.0006351768970489502</v>
+        <v>-0.000635191798210144</v>
       </c>
       <c r="JB30" t="n">
         <v>0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-7.360056042671204e-05</v>
+        <v>-7.363036274909973e-05</v>
       </c>
       <c r="JB31" t="n">
         <v>0.7199999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.0003075525164604187</v>
+        <v>-0.000307571142911911</v>
       </c>
       <c r="JB32" t="n">
         <v>0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.0003825798630714417</v>
+        <v>-0.0003826208412647247</v>
       </c>
       <c r="JB33" t="n">
         <v>0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.0005825720727443695</v>
+        <v>-0.000582568347454071</v>
       </c>
       <c r="JB34" t="n">
         <v>0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.0005738735198974609</v>
+        <v>-0.0005738586187362671</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.02000000000000007</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.0004628486931324005</v>
+        <v>-0.0004628337919712067</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.02000000000000007</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.0001195631921291351</v>
+        <v>-0.0001195557415485382</v>
       </c>
       <c r="JB37" t="n">
         <v>0.1199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.0005945265293121338</v>
+        <v>0.0005944855511188507</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.001320123672485352</v>
+        <v>0.001320112496614456</v>
       </c>
       <c r="JB40" t="n">
         <v>0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.001892492175102234</v>
+        <v>0.001892466098070145</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.002637226134538651</v>
+        <v>0.002637077122926712</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.002910833805799484</v>
+        <v>0.002910729497671127</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.003540072590112686</v>
+        <v>0.003539938479661942</v>
       </c>
       <c r="JB44" t="n">
         <v>0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.003219962120056152</v>
+        <v>0.003219347447156906</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.16</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.0001596100628376007</v>
+        <v>-0.0001600049436092377</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.002885580062866211</v>
+        <v>-0.002885904163122177</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.005471073091030121</v>
+        <v>-0.005471345037221909</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.006203126162290573</v>
+        <v>-0.006203137338161469</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.00642041489481926</v>
+        <v>-0.006420429795980453</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.005126237869262695</v>
+        <v>-0.005126282572746277</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.004634961485862732</v>
+        <v>-0.004635009914636612</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.00507669523358345</v>
+        <v>-0.005076773464679718</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.005259372293949127</v>
+        <v>-0.005259431898593903</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.005497049540281296</v>
+        <v>-0.005497120320796967</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.005204755812883377</v>
+        <v>-0.00520499050617218</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.004766102880239487</v>
+        <v>-0.004766140133142471</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.004298564046621323</v>
+        <v>-0.004298586398363113</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.003882508724927902</v>
+        <v>-0.003882512450218201</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.003662660717964172</v>
+        <v>-0.003662671893835068</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.003223203122615814</v>
+        <v>-0.003223206847906113</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.002829082310199738</v>
+        <v>-0.002829112112522125</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.1199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.002818945795297623</v>
+        <v>-0.00281892716884613</v>
       </c>
       <c r="JB66" t="n">
         <v>0.16</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.002250254154205322</v>
+        <v>-0.002250257879495621</v>
       </c>
       <c r="JB67" t="n">
         <v>0.1600000000000001</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.003146272152662277</v>
+        <v>-0.003146301954984665</v>
       </c>
       <c r="JB69" t="n">
         <v>0.16</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.003403868526220322</v>
+        <v>-0.003403909504413605</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.1199999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.003820683807134628</v>
+        <v>-0.003820709884166718</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.003910496830940247</v>
+        <v>-0.003910470753908157</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.003817055374383926</v>
+        <v>-0.003817062824964523</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.4399999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.001854255795478821</v>
+        <v>-0.001854237169027328</v>
       </c>
       <c r="JB74" t="n">
         <v>0.4399999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.002065662294626236</v>
+        <v>-0.002065595239400864</v>
       </c>
       <c r="JB75" t="n">
         <v>0.4399999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.003355506807565689</v>
+        <v>-0.003355484455823898</v>
       </c>
       <c r="JB76" t="n">
         <v>0.4399999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.004335477948188782</v>
+        <v>-0.004335392266511917</v>
       </c>
       <c r="JB77" t="n">
         <v>0.16</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.004356462508440018</v>
+        <v>-0.004356361925601959</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.1199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.004399742931127548</v>
+        <v>-0.004399668425321579</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.8599999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.004301086068153381</v>
+        <v>-0.004301078617572784</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.5799999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.003883343189954758</v>
+        <v>-0.00388336181640625</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.3</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.003523025661706924</v>
+        <v>-0.003523040562868118</v>
       </c>
       <c r="JB82" t="n">
         <v>0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.002988949418067932</v>
+        <v>-0.002988968044519424</v>
       </c>
       <c r="JB83" t="n">
         <v>0.8599999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.002690795809030533</v>
+        <v>-0.002690818160772324</v>
       </c>
       <c r="JB84" t="n">
         <v>0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.002415653318166733</v>
+        <v>-0.00241566076874733</v>
       </c>
       <c r="JB85" t="n">
         <v>0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.002366747707128525</v>
+        <v>-0.002366755157709122</v>
       </c>
       <c r="JB86" t="n">
         <v>0.9999999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.002559509128332138</v>
+        <v>-0.002559542655944824</v>
       </c>
       <c r="JB87" t="n">
         <v>0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.001953493803739548</v>
+        <v>-0.001953441649675369</v>
       </c>
       <c r="JB88" t="n">
         <v>0.9999999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.002156689763069153</v>
+        <v>-0.002156704664230347</v>
       </c>
       <c r="JB89" t="n">
         <v>0.8599999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.001661613583564758</v>
+        <v>-0.001661635935306549</v>
       </c>
       <c r="JB90" t="n">
         <v>0.7199999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.002380520105361938</v>
+        <v>-0.002380460500717163</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.02000000000000007</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.003091830760240555</v>
+        <v>-0.003091827034950256</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.5799999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.003423728048801422</v>
+        <v>-0.003423653542995453</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.5799999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.003512397408485413</v>
+        <v>-0.003512289375066757</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.5799999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.003206048160791397</v>
+        <v>-0.003206014633178711</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.5799999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.003179304301738739</v>
+        <v>-0.003179311752319336</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.3</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.003048095852136612</v>
+        <v>-0.003048125654459</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.02000000000000007</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.002320911735296249</v>
+        <v>-0.002320829778909683</v>
       </c>
       <c r="JB99" t="n">
         <v>0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.002178966999053955</v>
+        <v>-0.002179067581892014</v>
       </c>
       <c r="JB101" t="n">
         <v>0.8599999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.002704165875911713</v>
+        <v>-0.002704225480556488</v>
       </c>
       <c r="JB102" t="n">
         <v>0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.002961795777082443</v>
+        <v>-0.002961661666631699</v>
       </c>
       <c r="JB103" t="n">
         <v>0.5799999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.002982009202241898</v>
+        <v>-0.002981953322887421</v>
       </c>
       <c r="JB104" t="n">
         <v>0.3</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.003088101744651794</v>
+        <v>-0.003088094294071198</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.5799999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.003165923058986664</v>
+        <v>-0.00316590815782547</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.003813415765762329</v>
+        <v>-0.003813378512859344</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.003846459090709686</v>
+        <v>-0.003846351057291031</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.003479808568954468</v>
+        <v>-0.003479704260826111</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.003375127911567688</v>
+        <v>-0.003375150263309479</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.003229197114706039</v>
+        <v>-0.003229215741157532</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.8599999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.003047917038202286</v>
+        <v>-0.00304793193936348</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.5799999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.002762474119663239</v>
+        <v>-0.002762515097856522</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.002350185066461563</v>
+        <v>-0.002350207418203354</v>
       </c>
       <c r="JB115" t="n">
         <v>0.5799999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.002202562987804413</v>
+        <v>-0.00220247358083725</v>
       </c>
       <c r="JB116" t="n">
         <v>0.8599999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.002369016408920288</v>
+        <v>-0.002368882298469543</v>
       </c>
       <c r="JB117" t="n">
         <v>0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.002404466271400452</v>
+        <v>-0.002404414117336273</v>
       </c>
       <c r="JB118" t="n">
         <v>0.9999999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.002322204411029816</v>
+        <v>-0.002322215586900711</v>
       </c>
       <c r="JB120" t="n">
         <v>0.9999999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.002017851918935776</v>
+        <v>-0.002017837017774582</v>
       </c>
       <c r="JB121" t="n">
         <v>0.9999999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.002281248569488525</v>
+        <v>-0.002281252294778824</v>
       </c>
       <c r="JB122" t="n">
         <v>0.8599999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.002268847078084946</v>
+        <v>-0.002268824726343155</v>
       </c>
       <c r="JB123" t="n">
         <v>0.7199999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.002520866692066193</v>
+        <v>-0.00252087414264679</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.02000000000000007</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.002594590187072754</v>
+        <v>-0.002594616264104843</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.2300000000000003</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.002326879650354385</v>
+        <v>-0.002326883375644684</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.4400000000000004</v>
